--- a/guides/planilha_controle_de_estoque.xlsx
+++ b/guides/planilha_controle_de_estoque.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cadastro de Produtos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Entradas-Saidas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ponto de Pedido" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cadastro de Produtos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entradas-Saidas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ponto de Pedido" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suporte" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +31,16 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E4A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,9 +68,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -788,4 +801,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Duvidas ou sugestoes?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Siga a Skill Hub no Instagram:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>@skillhub.tec</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>